--- a/publisher-guides/Subscription-IG/output/all-profiles.xlsx
+++ b/publisher-guides/Subscription-IG/output/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24305" uniqueCount="1489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22762" uniqueCount="1470">
   <si>
     <t>Property</t>
   </si>
@@ -4747,64 +4747,6 @@
   </si>
   <si>
     <t>ISiK Subscription Status</t>
-  </si>
-  <si>
-    <t>test-patient</t>
-  </si>
-  <si>
-    <t>http://example.org/fhir/test-subscription-ig/StructureDefinition/test-patient</t>
-  </si>
-  <si>
-    <t>TestPatient</t>
-  </si>
-  <si>
-    <t>Test Patient Profile</t>
-  </si>
-  <si>
-    <t>draft</t>
-  </si>
-  <si>
-    <t>2025-08-12T10:16:22+02:00</t>
-  </si>
-  <si>
-    <t>A simple test patient profile for validation purposes</t>
-  </si>
-  <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
-  </si>
-  <si>
-    <t>Logical id of this artifact</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
-  </si>
-  <si>
-    <t>At least one identifier is required</t>
-  </si>
-  <si>
-    <t>Whether this patient's record is in active use</t>
-  </si>
-  <si>
-    <t>If a record is inactive, and linked to an active record, then future patient/record updates should occur on the other patient.</t>
-  </si>
-  <si>
-    <t>Patient name is required</t>
-  </si>
-  <si>
-    <t>The gender might not match the biological sex as determined by genetics or the individual's preferred identification. Note that for both humans and particularly animals, there are other legitimate possibilities than male and female, though the vast majority of systems and contexts only support male and female.  Systems providing decision support or enforcing business rules should ideally do this on the basis of Observations dealing with the specific sex or gender aspect of interest (anatomical, chromosomal, social, etc.)  However, because these observations are infrequently recorded, defaulting to the administrative gender is common practice.  Where such defaulting occurs, rule enforcement should allow for the variation between administrative and biological, chromosomal and other gender aspects.  For example, an alert about a hysterectomy on a male should be handled as a warning or overridable error, not a "hard" error.  See the Patient Gender and Sex section for additional information about communicating patient gender and sex.</t>
-  </si>
-  <si>
-    <t>The date of birth for the individual</t>
-  </si>
-  <si>
-    <t>At least an estimated year should be provided as a guess if the real DOB is unknown  There is a standard extension "patient-birthTime" available that should be used where Time is required (such as in maternity/infant care systems).</t>
-  </si>
-  <si>
-    <t>Link to another patient resource that concerns the same actual person</t>
-  </si>
-  <si>
-    <t>There is no assumption that linked patient records have mutual links.</t>
   </si>
 </sst>
 </file>
@@ -4938,7 +4880,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B167"/>
+  <dimension ref="A1:B147"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -6077,158 +6019,6 @@
         <v>38</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" t="s" s="1">
-        <v>0</v>
-      </c>
-      <c r="B148" t="s" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B149" t="s" s="2">
-        <v>1470</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="B150" t="s" s="2">
-        <v>1471</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="B151" t="s" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s" s="2">
-        <v>8</v>
-      </c>
-      <c r="B152" t="s" s="2">
-        <v>1472</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s" s="2">
-        <v>9</v>
-      </c>
-      <c r="B153" t="s" s="2">
-        <v>1473</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s" s="2">
-        <v>11</v>
-      </c>
-      <c r="B154" t="s" s="2">
-        <v>1474</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B155" s="2"/>
-    </row>
-    <row r="156">
-      <c r="A156" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s" s="2">
-        <v>1475</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="B157" s="2"/>
-    </row>
-    <row r="158">
-      <c r="A158" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B158" t="s" s="2">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B159" t="s" s="2">
-        <v>1476</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B160" s="2"/>
-    </row>
-    <row r="161">
-      <c r="A161" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B161" s="2"/>
-    </row>
-    <row r="162">
-      <c r="A162" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="B162" t="s" s="2">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B163" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B164" t="s" s="2">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B165" t="s" s="2">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B166" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B167" t="s" s="2">
-        <v>38</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -6236,7 +6026,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK727"/>
+  <dimension ref="A1:AK682"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.6875" customWidth="true" bestFit="true"/>
@@ -77784,4775 +77574,6 @@
         <v>23</v>
       </c>
     </row>
-    <row r="683">
-      <c r="A683" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B683" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="C683" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="D683" s="2"/>
-      <c r="E683" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="F683" s="2"/>
-      <c r="G683" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H683" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I683" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J683" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K683" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L683" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="M683" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="N683" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="O683" s="2"/>
-      <c r="P683" s="2"/>
-      <c r="Q683" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R683" s="2"/>
-      <c r="S683" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T683" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U683" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V683" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W683" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X683" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y683" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z683" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA683" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB683" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC683" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD683" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE683" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF683" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG683" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="AH683" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI683" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ683" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AK683" t="s" s="2">
-        <v>1477</v>
-      </c>
-    </row>
-    <row r="684">
-      <c r="A684" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B684" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="C684" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="D684" s="2"/>
-      <c r="E684" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F684" s="2"/>
-      <c r="G684" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H684" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I684" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J684" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K684" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L684" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="M684" t="s" s="2">
-        <v>1478</v>
-      </c>
-      <c r="N684" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="O684" t="s" s="2">
-        <v>1479</v>
-      </c>
-      <c r="P684" s="2"/>
-      <c r="Q684" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R684" s="2"/>
-      <c r="S684" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T684" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U684" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V684" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W684" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X684" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y684" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z684" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA684" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB684" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC684" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD684" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE684" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF684" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG684" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH684" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI684" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ684" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AK684" t="s" s="2">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="685">
-      <c r="A685" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B685" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="C685" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="D685" s="2"/>
-      <c r="E685" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F685" s="2"/>
-      <c r="G685" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H685" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I685" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J685" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K685" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L685" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="M685" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="N685" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="O685" s="2"/>
-      <c r="P685" s="2"/>
-      <c r="Q685" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R685" s="2"/>
-      <c r="S685" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T685" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U685" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V685" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W685" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X685" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y685" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z685" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA685" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB685" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC685" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD685" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE685" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF685" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG685" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH685" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI685" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ685" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK685" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="686">
-      <c r="A686" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B686" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="C686" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="D686" s="2"/>
-      <c r="E686" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F686" s="2"/>
-      <c r="G686" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H686" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I686" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J686" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K686" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L686" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="M686" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N686" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="O686" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="P686" s="2"/>
-      <c r="Q686" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R686" s="2"/>
-      <c r="S686" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T686" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U686" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V686" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W686" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X686" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y686" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z686" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA686" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB686" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC686" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD686" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE686" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF686" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG686" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="AH686" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI686" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ686" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK686" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="687">
-      <c r="A687" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B687" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="C687" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="D687" s="2"/>
-      <c r="E687" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F687" s="2"/>
-      <c r="G687" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H687" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I687" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J687" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K687" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L687" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="M687" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N687" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O687" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="P687" s="2"/>
-      <c r="Q687" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R687" s="2"/>
-      <c r="S687" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T687" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U687" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V687" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W687" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X687" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y687" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="Z687" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AA687" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AB687" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC687" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD687" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE687" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF687" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG687" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AH687" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI687" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ687" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK687" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="688">
-      <c r="A688" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B688" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="C688" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="D688" s="2"/>
-      <c r="E688" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="F688" s="2"/>
-      <c r="G688" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H688" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I688" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J688" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K688" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L688" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="M688" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="N688" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="O688" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="P688" s="2"/>
-      <c r="Q688" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R688" s="2"/>
-      <c r="S688" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T688" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U688" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V688" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W688" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X688" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y688" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z688" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA688" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB688" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC688" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD688" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE688" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF688" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG688" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="AH688" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI688" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ688" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK688" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="689">
-      <c r="A689" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B689" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="C689" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="D689" s="2"/>
-      <c r="E689" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="F689" s="2"/>
-      <c r="G689" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H689" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I689" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J689" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K689" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L689" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="M689" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="N689" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="O689" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="P689" s="2"/>
-      <c r="Q689" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R689" s="2"/>
-      <c r="S689" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T689" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U689" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V689" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W689" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X689" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y689" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z689" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA689" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB689" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC689" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD689" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE689" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF689" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG689" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="AH689" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI689" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ689" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AK689" t="s" s="2">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="690">
-      <c r="A690" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B690" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="C690" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="D690" s="2"/>
-      <c r="E690" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="F690" s="2"/>
-      <c r="G690" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H690" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I690" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J690" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K690" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L690" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="M690" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N690" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="O690" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="P690" s="2"/>
-      <c r="Q690" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R690" s="2"/>
-      <c r="S690" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T690" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U690" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V690" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W690" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X690" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y690" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z690" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA690" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB690" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC690" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AD690" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AE690" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF690" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AG690" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="AH690" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI690" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ690" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK690" t="s" s="2">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="691">
-      <c r="A691" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B691" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="C691" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="D691" s="2"/>
-      <c r="E691" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="F691" s="2"/>
-      <c r="G691" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H691" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I691" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J691" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K691" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L691" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="M691" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="N691" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="O691" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="P691" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="Q691" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R691" s="2"/>
-      <c r="S691" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T691" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U691" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V691" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W691" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X691" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y691" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z691" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA691" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB691" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC691" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AD691" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AE691" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF691" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AG691" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="AH691" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI691" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ691" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK691" t="s" s="2">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="692">
-      <c r="A692" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B692" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="C692" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="D692" s="2"/>
-      <c r="E692" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F692" s="2"/>
-      <c r="G692" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H692" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I692" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J692" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K692" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L692" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="M692" t="s" s="2">
-        <v>1480</v>
-      </c>
-      <c r="N692" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="O692" s="2"/>
-      <c r="P692" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="Q692" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R692" s="2"/>
-      <c r="S692" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T692" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U692" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V692" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W692" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X692" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y692" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z692" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA692" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB692" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC692" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD692" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE692" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF692" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG692" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="AH692" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI692" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ692" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK692" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="693">
-      <c r="A693" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B693" t="s" s="2">
-        <v>799</v>
-      </c>
-      <c r="C693" t="s" s="2">
-        <v>799</v>
-      </c>
-      <c r="D693" s="2"/>
-      <c r="E693" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F693" s="2"/>
-      <c r="G693" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H693" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I693" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J693" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K693" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L693" t="s" s="2">
-        <v>800</v>
-      </c>
-      <c r="M693" t="s" s="2">
-        <v>1481</v>
-      </c>
-      <c r="N693" t="s" s="2">
-        <v>802</v>
-      </c>
-      <c r="O693" t="s" s="2">
-        <v>1482</v>
-      </c>
-      <c r="P693" t="s" s="2">
-        <v>804</v>
-      </c>
-      <c r="Q693" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R693" t="s" s="2">
-        <v>805</v>
-      </c>
-      <c r="S693" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T693" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U693" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V693" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W693" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X693" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y693" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z693" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA693" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB693" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC693" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD693" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE693" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF693" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG693" t="s" s="2">
-        <v>799</v>
-      </c>
-      <c r="AH693" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI693" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ693" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK693" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="694">
-      <c r="A694" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B694" t="s" s="2">
-        <v>806</v>
-      </c>
-      <c r="C694" t="s" s="2">
-        <v>806</v>
-      </c>
-      <c r="D694" s="2"/>
-      <c r="E694" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F694" s="2"/>
-      <c r="G694" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H694" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I694" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J694" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K694" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L694" t="s" s="2">
-        <v>807</v>
-      </c>
-      <c r="M694" t="s" s="2">
-        <v>1483</v>
-      </c>
-      <c r="N694" t="s" s="2">
-        <v>809</v>
-      </c>
-      <c r="O694" t="s" s="2">
-        <v>810</v>
-      </c>
-      <c r="P694" t="s" s="2">
-        <v>811</v>
-      </c>
-      <c r="Q694" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R694" s="2"/>
-      <c r="S694" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T694" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U694" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V694" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W694" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X694" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y694" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z694" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA694" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB694" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC694" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD694" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE694" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF694" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG694" t="s" s="2">
-        <v>806</v>
-      </c>
-      <c r="AH694" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI694" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ694" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK694" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="695">
-      <c r="A695" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B695" t="s" s="2">
-        <v>949</v>
-      </c>
-      <c r="C695" t="s" s="2">
-        <v>949</v>
-      </c>
-      <c r="D695" s="2"/>
-      <c r="E695" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F695" s="2"/>
-      <c r="G695" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H695" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I695" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J695" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K695" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L695" t="s" s="2">
-        <v>950</v>
-      </c>
-      <c r="M695" t="s" s="2">
-        <v>951</v>
-      </c>
-      <c r="N695" t="s" s="2">
-        <v>952</v>
-      </c>
-      <c r="O695" t="s" s="2">
-        <v>953</v>
-      </c>
-      <c r="P695" t="s" s="2">
-        <v>954</v>
-      </c>
-      <c r="Q695" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R695" s="2"/>
-      <c r="S695" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T695" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U695" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V695" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W695" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X695" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y695" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z695" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA695" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB695" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC695" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD695" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE695" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF695" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG695" t="s" s="2">
-        <v>949</v>
-      </c>
-      <c r="AH695" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI695" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ695" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK695" t="s" s="2">
-        <v>955</v>
-      </c>
-    </row>
-    <row r="696">
-      <c r="A696" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B696" t="s" s="2">
-        <v>991</v>
-      </c>
-      <c r="C696" t="s" s="2">
-        <v>991</v>
-      </c>
-      <c r="D696" s="2"/>
-      <c r="E696" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F696" s="2"/>
-      <c r="G696" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H696" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I696" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J696" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K696" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L696" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="M696" t="s" s="2">
-        <v>1248</v>
-      </c>
-      <c r="N696" t="s" s="2">
-        <v>993</v>
-      </c>
-      <c r="O696" t="s" s="2">
-        <v>1484</v>
-      </c>
-      <c r="P696" t="s" s="2">
-        <v>995</v>
-      </c>
-      <c r="Q696" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R696" s="2"/>
-      <c r="S696" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T696" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U696" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V696" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W696" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X696" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y696" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Z696" t="s" s="2">
-        <v>996</v>
-      </c>
-      <c r="AA696" t="s" s="2">
-        <v>997</v>
-      </c>
-      <c r="AB696" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC696" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD696" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE696" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF696" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG696" t="s" s="2">
-        <v>991</v>
-      </c>
-      <c r="AH696" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI696" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ696" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK696" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="697">
-      <c r="A697" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B697" t="s" s="2">
-        <v>1008</v>
-      </c>
-      <c r="C697" t="s" s="2">
-        <v>1008</v>
-      </c>
-      <c r="D697" s="2"/>
-      <c r="E697" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F697" s="2"/>
-      <c r="G697" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H697" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I697" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J697" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K697" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L697" t="s" s="2">
-        <v>1009</v>
-      </c>
-      <c r="M697" t="s" s="2">
-        <v>1485</v>
-      </c>
-      <c r="N697" t="s" s="2">
-        <v>1011</v>
-      </c>
-      <c r="O697" t="s" s="2">
-        <v>1486</v>
-      </c>
-      <c r="P697" t="s" s="2">
-        <v>1013</v>
-      </c>
-      <c r="Q697" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R697" s="2"/>
-      <c r="S697" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T697" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U697" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V697" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W697" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X697" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y697" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z697" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA697" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB697" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC697" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD697" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE697" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF697" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG697" t="s" s="2">
-        <v>1008</v>
-      </c>
-      <c r="AH697" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI697" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ697" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK697" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="698">
-      <c r="A698" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B698" t="s" s="2">
-        <v>1036</v>
-      </c>
-      <c r="C698" t="s" s="2">
-        <v>1036</v>
-      </c>
-      <c r="D698" s="2"/>
-      <c r="E698" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F698" s="2"/>
-      <c r="G698" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H698" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I698" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J698" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K698" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L698" t="s" s="2">
-        <v>1037</v>
-      </c>
-      <c r="M698" t="s" s="2">
-        <v>1038</v>
-      </c>
-      <c r="N698" t="s" s="2">
-        <v>1039</v>
-      </c>
-      <c r="O698" t="s" s="2">
-        <v>1040</v>
-      </c>
-      <c r="P698" t="s" s="2">
-        <v>1041</v>
-      </c>
-      <c r="Q698" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R698" s="2"/>
-      <c r="S698" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T698" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U698" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V698" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W698" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X698" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y698" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z698" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA698" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB698" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC698" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD698" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE698" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF698" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG698" t="s" s="2">
-        <v>1036</v>
-      </c>
-      <c r="AH698" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI698" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ698" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK698" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="699">
-      <c r="A699" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B699" t="s" s="2">
-        <v>1042</v>
-      </c>
-      <c r="C699" t="s" s="2">
-        <v>1042</v>
-      </c>
-      <c r="D699" s="2"/>
-      <c r="E699" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F699" s="2"/>
-      <c r="G699" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H699" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I699" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J699" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K699" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L699" t="s" s="2">
-        <v>1043</v>
-      </c>
-      <c r="M699" t="s" s="2">
-        <v>1044</v>
-      </c>
-      <c r="N699" t="s" s="2">
-        <v>1045</v>
-      </c>
-      <c r="O699" t="s" s="2">
-        <v>1046</v>
-      </c>
-      <c r="P699" t="s" s="2">
-        <v>1047</v>
-      </c>
-      <c r="Q699" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R699" s="2"/>
-      <c r="S699" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T699" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U699" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V699" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W699" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X699" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y699" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z699" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA699" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB699" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC699" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD699" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE699" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF699" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG699" t="s" s="2">
-        <v>1042</v>
-      </c>
-      <c r="AH699" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI699" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ699" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK699" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="700">
-      <c r="A700" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B700" t="s" s="2">
-        <v>1198</v>
-      </c>
-      <c r="C700" t="s" s="2">
-        <v>1198</v>
-      </c>
-      <c r="D700" s="2"/>
-      <c r="E700" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F700" s="2"/>
-      <c r="G700" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H700" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I700" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J700" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K700" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L700" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="M700" t="s" s="2">
-        <v>1199</v>
-      </c>
-      <c r="N700" t="s" s="2">
-        <v>1200</v>
-      </c>
-      <c r="O700" t="s" s="2">
-        <v>1201</v>
-      </c>
-      <c r="P700" t="s" s="2">
-        <v>1202</v>
-      </c>
-      <c r="Q700" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R700" s="2"/>
-      <c r="S700" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T700" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U700" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V700" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W700" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X700" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y700" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="Z700" t="s" s="2">
-        <v>1203</v>
-      </c>
-      <c r="AA700" t="s" s="2">
-        <v>1204</v>
-      </c>
-      <c r="AB700" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC700" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD700" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE700" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF700" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG700" t="s" s="2">
-        <v>1198</v>
-      </c>
-      <c r="AH700" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI700" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ700" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK700" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="701">
-      <c r="A701" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B701" t="s" s="2">
-        <v>1205</v>
-      </c>
-      <c r="C701" t="s" s="2">
-        <v>1205</v>
-      </c>
-      <c r="D701" s="2"/>
-      <c r="E701" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F701" s="2"/>
-      <c r="G701" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H701" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I701" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J701" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K701" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L701" t="s" s="2">
-        <v>1206</v>
-      </c>
-      <c r="M701" t="s" s="2">
-        <v>1207</v>
-      </c>
-      <c r="N701" t="s" s="2">
-        <v>1208</v>
-      </c>
-      <c r="O701" t="s" s="2">
-        <v>1209</v>
-      </c>
-      <c r="P701" t="s" s="2">
-        <v>1210</v>
-      </c>
-      <c r="Q701" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R701" s="2"/>
-      <c r="S701" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T701" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U701" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V701" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W701" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X701" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y701" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z701" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA701" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB701" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC701" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD701" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE701" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF701" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG701" t="s" s="2">
-        <v>1205</v>
-      </c>
-      <c r="AH701" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI701" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ701" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK701" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="702">
-      <c r="A702" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B702" t="s" s="2">
-        <v>1211</v>
-      </c>
-      <c r="C702" t="s" s="2">
-        <v>1211</v>
-      </c>
-      <c r="D702" s="2"/>
-      <c r="E702" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F702" s="2"/>
-      <c r="G702" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H702" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I702" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J702" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K702" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L702" t="s" s="2">
-        <v>1212</v>
-      </c>
-      <c r="M702" t="s" s="2">
-        <v>1213</v>
-      </c>
-      <c r="N702" t="s" s="2">
-        <v>1214</v>
-      </c>
-      <c r="O702" t="s" s="2">
-        <v>1215</v>
-      </c>
-      <c r="P702" t="s" s="2">
-        <v>1216</v>
-      </c>
-      <c r="Q702" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R702" s="2"/>
-      <c r="S702" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T702" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U702" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V702" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W702" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X702" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y702" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z702" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA702" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB702" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC702" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD702" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE702" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF702" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG702" t="s" s="2">
-        <v>1211</v>
-      </c>
-      <c r="AH702" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI702" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ702" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK702" t="s" s="2">
-        <v>1217</v>
-      </c>
-    </row>
-    <row r="703">
-      <c r="A703" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B703" t="s" s="2">
-        <v>1218</v>
-      </c>
-      <c r="C703" t="s" s="2">
-        <v>1218</v>
-      </c>
-      <c r="D703" s="2"/>
-      <c r="E703" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F703" s="2"/>
-      <c r="G703" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H703" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I703" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J703" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K703" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L703" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="M703" t="s" s="2">
-        <v>1219</v>
-      </c>
-      <c r="N703" t="s" s="2">
-        <v>1220</v>
-      </c>
-      <c r="O703" t="s" s="2">
-        <v>1221</v>
-      </c>
-      <c r="P703" t="s" s="2">
-        <v>1222</v>
-      </c>
-      <c r="Q703" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R703" s="2"/>
-      <c r="S703" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T703" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U703" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V703" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W703" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X703" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y703" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z703" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA703" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB703" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC703" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD703" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE703" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF703" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG703" t="s" s="2">
-        <v>1218</v>
-      </c>
-      <c r="AH703" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI703" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ703" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK703" t="s" s="2">
-        <v>1223</v>
-      </c>
-    </row>
-    <row r="704">
-      <c r="A704" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B704" t="s" s="2">
-        <v>1224</v>
-      </c>
-      <c r="C704" t="s" s="2">
-        <v>1224</v>
-      </c>
-      <c r="D704" s="2"/>
-      <c r="E704" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F704" s="2"/>
-      <c r="G704" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H704" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I704" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J704" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K704" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L704" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="M704" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="N704" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="O704" s="2"/>
-      <c r="P704" s="2"/>
-      <c r="Q704" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R704" s="2"/>
-      <c r="S704" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T704" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U704" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V704" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W704" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X704" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y704" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z704" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA704" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB704" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC704" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD704" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE704" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF704" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG704" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AH704" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI704" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ704" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AK704" t="s" s="2">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="705">
-      <c r="A705" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B705" t="s" s="2">
-        <v>1225</v>
-      </c>
-      <c r="C705" t="s" s="2">
-        <v>1225</v>
-      </c>
-      <c r="D705" s="2"/>
-      <c r="E705" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="F705" s="2"/>
-      <c r="G705" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H705" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I705" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J705" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K705" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L705" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="M705" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N705" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="O705" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="P705" s="2"/>
-      <c r="Q705" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R705" s="2"/>
-      <c r="S705" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T705" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U705" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V705" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W705" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X705" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y705" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z705" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA705" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB705" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC705" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AD705" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AE705" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF705" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AG705" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AH705" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI705" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ705" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK705" t="s" s="2">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="706">
-      <c r="A706" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B706" t="s" s="2">
-        <v>1226</v>
-      </c>
-      <c r="C706" t="s" s="2">
-        <v>1226</v>
-      </c>
-      <c r="D706" s="2"/>
-      <c r="E706" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="F706" s="2"/>
-      <c r="G706" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H706" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I706" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J706" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K706" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L706" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="M706" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N706" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="O706" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="P706" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="Q706" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R706" s="2"/>
-      <c r="S706" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T706" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U706" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V706" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W706" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X706" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y706" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z706" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA706" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB706" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC706" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD706" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE706" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF706" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG706" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AH706" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI706" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ706" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK706" t="s" s="2">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="707">
-      <c r="A707" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B707" t="s" s="2">
-        <v>1227</v>
-      </c>
-      <c r="C707" t="s" s="2">
-        <v>1227</v>
-      </c>
-      <c r="D707" s="2"/>
-      <c r="E707" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F707" s="2"/>
-      <c r="G707" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H707" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I707" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J707" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K707" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L707" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="M707" t="s" s="2">
-        <v>1228</v>
-      </c>
-      <c r="N707" t="s" s="2">
-        <v>1229</v>
-      </c>
-      <c r="O707" t="s" s="2">
-        <v>1201</v>
-      </c>
-      <c r="P707" t="s" s="2">
-        <v>1230</v>
-      </c>
-      <c r="Q707" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R707" s="2"/>
-      <c r="S707" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T707" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U707" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V707" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W707" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X707" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y707" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="Z707" t="s" s="2">
-        <v>1231</v>
-      </c>
-      <c r="AA707" t="s" s="2">
-        <v>1232</v>
-      </c>
-      <c r="AB707" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC707" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD707" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE707" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF707" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG707" t="s" s="2">
-        <v>1227</v>
-      </c>
-      <c r="AH707" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI707" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ707" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK707" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="708">
-      <c r="A708" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B708" t="s" s="2">
-        <v>1233</v>
-      </c>
-      <c r="C708" t="s" s="2">
-        <v>1233</v>
-      </c>
-      <c r="D708" s="2"/>
-      <c r="E708" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F708" s="2"/>
-      <c r="G708" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H708" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I708" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J708" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K708" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L708" t="s" s="2">
-        <v>807</v>
-      </c>
-      <c r="M708" t="s" s="2">
-        <v>1234</v>
-      </c>
-      <c r="N708" t="s" s="2">
-        <v>1235</v>
-      </c>
-      <c r="O708" t="s" s="2">
-        <v>1236</v>
-      </c>
-      <c r="P708" t="s" s="2">
-        <v>1237</v>
-      </c>
-      <c r="Q708" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R708" s="2"/>
-      <c r="S708" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T708" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U708" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V708" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W708" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X708" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y708" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z708" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA708" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB708" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC708" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD708" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE708" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF708" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG708" t="s" s="2">
-        <v>1233</v>
-      </c>
-      <c r="AH708" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI708" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ708" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK708" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="709">
-      <c r="A709" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B709" t="s" s="2">
-        <v>1238</v>
-      </c>
-      <c r="C709" t="s" s="2">
-        <v>1238</v>
-      </c>
-      <c r="D709" s="2"/>
-      <c r="E709" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F709" s="2"/>
-      <c r="G709" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H709" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I709" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J709" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K709" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L709" t="s" s="2">
-        <v>950</v>
-      </c>
-      <c r="M709" t="s" s="2">
-        <v>1239</v>
-      </c>
-      <c r="N709" t="s" s="2">
-        <v>1240</v>
-      </c>
-      <c r="O709" t="s" s="2">
-        <v>1241</v>
-      </c>
-      <c r="P709" t="s" s="2">
-        <v>954</v>
-      </c>
-      <c r="Q709" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R709" s="2"/>
-      <c r="S709" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T709" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U709" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V709" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W709" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X709" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y709" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z709" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA709" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB709" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC709" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD709" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE709" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF709" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG709" t="s" s="2">
-        <v>1238</v>
-      </c>
-      <c r="AH709" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI709" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ709" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK709" t="s" s="2">
-        <v>955</v>
-      </c>
-    </row>
-    <row r="710">
-      <c r="A710" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B710" t="s" s="2">
-        <v>1242</v>
-      </c>
-      <c r="C710" t="s" s="2">
-        <v>1242</v>
-      </c>
-      <c r="D710" s="2"/>
-      <c r="E710" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F710" s="2"/>
-      <c r="G710" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H710" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I710" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J710" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K710" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L710" t="s" s="2">
-        <v>1043</v>
-      </c>
-      <c r="M710" t="s" s="2">
-        <v>1243</v>
-      </c>
-      <c r="N710" t="s" s="2">
-        <v>1244</v>
-      </c>
-      <c r="O710" t="s" s="2">
-        <v>1245</v>
-      </c>
-      <c r="P710" t="s" s="2">
-        <v>1246</v>
-      </c>
-      <c r="Q710" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R710" s="2"/>
-      <c r="S710" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T710" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U710" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V710" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W710" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X710" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y710" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z710" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA710" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB710" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC710" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD710" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE710" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF710" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG710" t="s" s="2">
-        <v>1242</v>
-      </c>
-      <c r="AH710" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI710" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ710" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK710" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="711">
-      <c r="A711" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B711" t="s" s="2">
-        <v>1247</v>
-      </c>
-      <c r="C711" t="s" s="2">
-        <v>1247</v>
-      </c>
-      <c r="D711" s="2"/>
-      <c r="E711" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F711" s="2"/>
-      <c r="G711" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H711" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I711" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J711" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K711" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L711" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="M711" t="s" s="2">
-        <v>1248</v>
-      </c>
-      <c r="N711" t="s" s="2">
-        <v>1249</v>
-      </c>
-      <c r="O711" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="P711" t="s" s="2">
-        <v>1250</v>
-      </c>
-      <c r="Q711" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R711" s="2"/>
-      <c r="S711" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T711" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U711" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V711" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W711" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X711" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y711" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Z711" t="s" s="2">
-        <v>996</v>
-      </c>
-      <c r="AA711" t="s" s="2">
-        <v>997</v>
-      </c>
-      <c r="AB711" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC711" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD711" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE711" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF711" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG711" t="s" s="2">
-        <v>1247</v>
-      </c>
-      <c r="AH711" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI711" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ711" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK711" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="712">
-      <c r="A712" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B712" t="s" s="2">
-        <v>1251</v>
-      </c>
-      <c r="C712" t="s" s="2">
-        <v>1251</v>
-      </c>
-      <c r="D712" s="2"/>
-      <c r="E712" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F712" s="2"/>
-      <c r="G712" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H712" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I712" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J712" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K712" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L712" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="M712" t="s" s="2">
-        <v>1252</v>
-      </c>
-      <c r="N712" t="s" s="2">
-        <v>1253</v>
-      </c>
-      <c r="O712" t="s" s="2">
-        <v>1254</v>
-      </c>
-      <c r="P712" t="s" s="2">
-        <v>1255</v>
-      </c>
-      <c r="Q712" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R712" s="2"/>
-      <c r="S712" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T712" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U712" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V712" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W712" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X712" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y712" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z712" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA712" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB712" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC712" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD712" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE712" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF712" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG712" t="s" s="2">
-        <v>1251</v>
-      </c>
-      <c r="AH712" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI712" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ712" t="s" s="2">
-        <v>1256</v>
-      </c>
-      <c r="AK712" t="s" s="2">
-        <v>1257</v>
-      </c>
-    </row>
-    <row r="713">
-      <c r="A713" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B713" t="s" s="2">
-        <v>1258</v>
-      </c>
-      <c r="C713" t="s" s="2">
-        <v>1258</v>
-      </c>
-      <c r="D713" s="2"/>
-      <c r="E713" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F713" s="2"/>
-      <c r="G713" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H713" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I713" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J713" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K713" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L713" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="M713" t="s" s="2">
-        <v>1259</v>
-      </c>
-      <c r="N713" t="s" s="2">
-        <v>1260</v>
-      </c>
-      <c r="O713" t="s" s="2">
-        <v>988</v>
-      </c>
-      <c r="P713" s="2"/>
-      <c r="Q713" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R713" s="2"/>
-      <c r="S713" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T713" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U713" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V713" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W713" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X713" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y713" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z713" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA713" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB713" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC713" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD713" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE713" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF713" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG713" t="s" s="2">
-        <v>1258</v>
-      </c>
-      <c r="AH713" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI713" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ713" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK713" t="s" s="2">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="714">
-      <c r="A714" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B714" t="s" s="2">
-        <v>1261</v>
-      </c>
-      <c r="C714" t="s" s="2">
-        <v>1261</v>
-      </c>
-      <c r="D714" s="2"/>
-      <c r="E714" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F714" s="2"/>
-      <c r="G714" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H714" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I714" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J714" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K714" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L714" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="M714" t="s" s="2">
-        <v>1262</v>
-      </c>
-      <c r="N714" t="s" s="2">
-        <v>1263</v>
-      </c>
-      <c r="O714" t="s" s="2">
-        <v>1264</v>
-      </c>
-      <c r="P714" t="s" s="2">
-        <v>1265</v>
-      </c>
-      <c r="Q714" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R714" s="2"/>
-      <c r="S714" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T714" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U714" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V714" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W714" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X714" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y714" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z714" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA714" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB714" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC714" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD714" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE714" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF714" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG714" t="s" s="2">
-        <v>1261</v>
-      </c>
-      <c r="AH714" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI714" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ714" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK714" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="715">
-      <c r="A715" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B715" t="s" s="2">
-        <v>1266</v>
-      </c>
-      <c r="C715" t="s" s="2">
-        <v>1266</v>
-      </c>
-      <c r="D715" s="2"/>
-      <c r="E715" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F715" s="2"/>
-      <c r="G715" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H715" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I715" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J715" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K715" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L715" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="M715" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="N715" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="O715" s="2"/>
-      <c r="P715" s="2"/>
-      <c r="Q715" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R715" s="2"/>
-      <c r="S715" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T715" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U715" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V715" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W715" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X715" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y715" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z715" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA715" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB715" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC715" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD715" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE715" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF715" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG715" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AH715" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI715" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ715" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AK715" t="s" s="2">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="716">
-      <c r="A716" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B716" t="s" s="2">
-        <v>1267</v>
-      </c>
-      <c r="C716" t="s" s="2">
-        <v>1267</v>
-      </c>
-      <c r="D716" s="2"/>
-      <c r="E716" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="F716" s="2"/>
-      <c r="G716" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H716" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I716" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J716" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K716" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L716" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="M716" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N716" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="O716" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="P716" s="2"/>
-      <c r="Q716" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R716" s="2"/>
-      <c r="S716" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T716" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U716" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V716" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W716" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X716" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y716" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z716" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA716" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB716" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC716" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AD716" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AE716" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF716" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AG716" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AH716" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI716" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ716" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK716" t="s" s="2">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="717">
-      <c r="A717" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B717" t="s" s="2">
-        <v>1268</v>
-      </c>
-      <c r="C717" t="s" s="2">
-        <v>1268</v>
-      </c>
-      <c r="D717" s="2"/>
-      <c r="E717" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="F717" s="2"/>
-      <c r="G717" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H717" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I717" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J717" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K717" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L717" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="M717" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N717" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="O717" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="P717" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="Q717" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R717" s="2"/>
-      <c r="S717" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T717" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U717" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V717" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W717" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X717" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y717" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z717" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA717" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB717" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC717" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD717" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE717" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF717" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG717" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AH717" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI717" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ717" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK717" t="s" s="2">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="718">
-      <c r="A718" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B718" t="s" s="2">
-        <v>1269</v>
-      </c>
-      <c r="C718" t="s" s="2">
-        <v>1269</v>
-      </c>
-      <c r="D718" s="2"/>
-      <c r="E718" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F718" s="2"/>
-      <c r="G718" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H718" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I718" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J718" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K718" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L718" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="M718" t="s" s="2">
-        <v>1270</v>
-      </c>
-      <c r="N718" t="s" s="2">
-        <v>1271</v>
-      </c>
-      <c r="O718" t="s" s="2">
-        <v>1272</v>
-      </c>
-      <c r="P718" t="s" s="2">
-        <v>1273</v>
-      </c>
-      <c r="Q718" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R718" s="2"/>
-      <c r="S718" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T718" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U718" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V718" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W718" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X718" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y718" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="Z718" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AA718" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AB718" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC718" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD718" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE718" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF718" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG718" t="s" s="2">
-        <v>1269</v>
-      </c>
-      <c r="AH718" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI718" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ718" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK718" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="719">
-      <c r="A719" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B719" t="s" s="2">
-        <v>1274</v>
-      </c>
-      <c r="C719" t="s" s="2">
-        <v>1274</v>
-      </c>
-      <c r="D719" s="2"/>
-      <c r="E719" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F719" s="2"/>
-      <c r="G719" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H719" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I719" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J719" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K719" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L719" t="s" s="2">
-        <v>800</v>
-      </c>
-      <c r="M719" t="s" s="2">
-        <v>1275</v>
-      </c>
-      <c r="N719" t="s" s="2">
-        <v>1276</v>
-      </c>
-      <c r="O719" t="s" s="2">
-        <v>1277</v>
-      </c>
-      <c r="P719" t="s" s="2">
-        <v>1278</v>
-      </c>
-      <c r="Q719" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R719" s="2"/>
-      <c r="S719" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T719" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U719" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V719" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W719" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X719" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y719" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z719" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA719" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB719" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC719" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD719" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE719" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF719" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG719" t="s" s="2">
-        <v>1274</v>
-      </c>
-      <c r="AH719" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI719" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ719" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK719" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="720">
-      <c r="A720" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B720" t="s" s="2">
-        <v>1279</v>
-      </c>
-      <c r="C720" t="s" s="2">
-        <v>1279</v>
-      </c>
-      <c r="D720" s="2"/>
-      <c r="E720" t="s" s="2">
-        <v>1280</v>
-      </c>
-      <c r="F720" s="2"/>
-      <c r="G720" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H720" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I720" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J720" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K720" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L720" t="s" s="2">
-        <v>1281</v>
-      </c>
-      <c r="M720" t="s" s="2">
-        <v>1282</v>
-      </c>
-      <c r="N720" t="s" s="2">
-        <v>1283</v>
-      </c>
-      <c r="O720" t="s" s="2">
-        <v>1284</v>
-      </c>
-      <c r="P720" s="2"/>
-      <c r="Q720" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R720" s="2"/>
-      <c r="S720" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T720" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U720" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V720" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W720" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X720" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y720" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z720" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA720" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB720" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC720" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD720" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE720" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF720" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG720" t="s" s="2">
-        <v>1279</v>
-      </c>
-      <c r="AH720" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI720" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ720" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK720" t="s" s="2">
-        <v>1257</v>
-      </c>
-    </row>
-    <row r="721">
-      <c r="A721" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B721" t="s" s="2">
-        <v>1285</v>
-      </c>
-      <c r="C721" t="s" s="2">
-        <v>1285</v>
-      </c>
-      <c r="D721" s="2"/>
-      <c r="E721" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F721" s="2"/>
-      <c r="G721" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H721" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I721" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J721" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K721" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L721" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="M721" t="s" s="2">
-        <v>1286</v>
-      </c>
-      <c r="N721" t="s" s="2">
-        <v>1287</v>
-      </c>
-      <c r="O721" t="s" s="2">
-        <v>1288</v>
-      </c>
-      <c r="P721" t="s" s="2">
-        <v>1289</v>
-      </c>
-      <c r="Q721" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R721" s="2"/>
-      <c r="S721" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T721" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U721" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V721" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W721" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X721" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y721" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z721" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA721" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB721" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC721" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD721" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE721" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF721" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG721" t="s" s="2">
-        <v>1285</v>
-      </c>
-      <c r="AH721" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI721" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ721" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK721" t="s" s="2">
-        <v>1257</v>
-      </c>
-    </row>
-    <row r="722">
-      <c r="A722" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B722" t="s" s="2">
-        <v>1290</v>
-      </c>
-      <c r="C722" t="s" s="2">
-        <v>1290</v>
-      </c>
-      <c r="D722" s="2"/>
-      <c r="E722" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F722" s="2"/>
-      <c r="G722" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H722" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I722" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J722" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K722" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L722" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="M722" t="s" s="2">
-        <v>1487</v>
-      </c>
-      <c r="N722" t="s" s="2">
-        <v>1292</v>
-      </c>
-      <c r="O722" t="s" s="2">
-        <v>1488</v>
-      </c>
-      <c r="P722" t="s" s="2">
-        <v>1294</v>
-      </c>
-      <c r="Q722" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R722" s="2"/>
-      <c r="S722" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T722" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U722" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V722" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W722" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X722" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y722" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z722" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA722" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB722" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC722" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD722" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE722" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF722" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG722" t="s" s="2">
-        <v>1290</v>
-      </c>
-      <c r="AH722" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI722" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ722" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK722" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="723">
-      <c r="A723" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B723" t="s" s="2">
-        <v>1295</v>
-      </c>
-      <c r="C723" t="s" s="2">
-        <v>1295</v>
-      </c>
-      <c r="D723" s="2"/>
-      <c r="E723" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F723" s="2"/>
-      <c r="G723" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H723" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I723" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J723" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K723" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L723" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="M723" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="N723" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="O723" s="2"/>
-      <c r="P723" s="2"/>
-      <c r="Q723" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R723" s="2"/>
-      <c r="S723" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T723" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U723" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V723" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W723" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X723" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y723" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z723" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA723" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB723" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC723" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD723" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE723" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF723" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG723" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AH723" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI723" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ723" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AK723" t="s" s="2">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="724">
-      <c r="A724" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B724" t="s" s="2">
-        <v>1296</v>
-      </c>
-      <c r="C724" t="s" s="2">
-        <v>1296</v>
-      </c>
-      <c r="D724" s="2"/>
-      <c r="E724" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="F724" s="2"/>
-      <c r="G724" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H724" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I724" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J724" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K724" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L724" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="M724" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N724" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="O724" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="P724" s="2"/>
-      <c r="Q724" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R724" s="2"/>
-      <c r="S724" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T724" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U724" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V724" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W724" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X724" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y724" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z724" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA724" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB724" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC724" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AD724" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AE724" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF724" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AG724" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AH724" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI724" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ724" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK724" t="s" s="2">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="725">
-      <c r="A725" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B725" t="s" s="2">
-        <v>1297</v>
-      </c>
-      <c r="C725" t="s" s="2">
-        <v>1297</v>
-      </c>
-      <c r="D725" s="2"/>
-      <c r="E725" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="F725" s="2"/>
-      <c r="G725" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H725" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I725" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J725" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K725" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L725" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="M725" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N725" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="O725" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="P725" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="Q725" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R725" s="2"/>
-      <c r="S725" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T725" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U725" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V725" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W725" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X725" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y725" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z725" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA725" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB725" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC725" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD725" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE725" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF725" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG725" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AH725" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI725" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ725" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK725" t="s" s="2">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="726">
-      <c r="A726" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B726" t="s" s="2">
-        <v>1298</v>
-      </c>
-      <c r="C726" t="s" s="2">
-        <v>1298</v>
-      </c>
-      <c r="D726" s="2"/>
-      <c r="E726" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F726" s="2"/>
-      <c r="G726" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H726" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I726" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J726" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K726" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L726" t="s" s="2">
-        <v>1299</v>
-      </c>
-      <c r="M726" t="s" s="2">
-        <v>1300</v>
-      </c>
-      <c r="N726" t="s" s="2">
-        <v>1301</v>
-      </c>
-      <c r="O726" t="s" s="2">
-        <v>1302</v>
-      </c>
-      <c r="P726" s="2"/>
-      <c r="Q726" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R726" s="2"/>
-      <c r="S726" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T726" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U726" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V726" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W726" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X726" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y726" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z726" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA726" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB726" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC726" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD726" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE726" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF726" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG726" t="s" s="2">
-        <v>1298</v>
-      </c>
-      <c r="AH726" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI726" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ726" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK726" t="s" s="2">
-        <v>1257</v>
-      </c>
-    </row>
-    <row r="727">
-      <c r="A727" t="s" s="2">
-        <v>1470</v>
-      </c>
-      <c r="B727" t="s" s="2">
-        <v>1315</v>
-      </c>
-      <c r="C727" t="s" s="2">
-        <v>1315</v>
-      </c>
-      <c r="D727" s="2"/>
-      <c r="E727" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F727" s="2"/>
-      <c r="G727" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H727" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I727" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J727" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K727" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L727" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="M727" t="s" s="2">
-        <v>1316</v>
-      </c>
-      <c r="N727" t="s" s="2">
-        <v>1317</v>
-      </c>
-      <c r="O727" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="P727" s="2"/>
-      <c r="Q727" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R727" s="2"/>
-      <c r="S727" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T727" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U727" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V727" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W727" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X727" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y727" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Z727" t="s" s="2">
-        <v>1317</v>
-      </c>
-      <c r="AA727" t="s" s="2">
-        <v>1318</v>
-      </c>
-      <c r="AB727" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC727" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD727" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE727" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF727" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG727" t="s" s="2">
-        <v>1315</v>
-      </c>
-      <c r="AH727" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI727" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ727" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK727" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
